--- a/Output/Models/Exposure_models_malf_div10_Femenino.xlsx
+++ b/Output/Models/Exposure_models_malf_div10_Femenino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.033991556497982</v>
+        <v>1.037582626080788</v>
       </c>
       <c r="C3">
-        <v>0.03959745840760348</v>
+        <v>0.04033449955041728</v>
       </c>
       <c r="D3">
-        <v>0.8441604975280699</v>
+        <v>0.9146911442765253</v>
       </c>
       <c r="E3">
-        <v>0.3985797252745103</v>
+        <v>0.3603537946979311</v>
       </c>
       <c r="F3">
-        <v>0.9567788679828326</v>
+        <v>0.9587158397660333</v>
       </c>
       <c r="G3">
-        <v>1.117435360129946</v>
+        <v>1.122937226329163</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.9892091255162186</v>
+        <v>0.9843557248577381</v>
       </c>
       <c r="C4">
-        <v>0.03968474879284488</v>
+        <v>0.0410540808351218</v>
       </c>
       <c r="D4">
-        <v>-0.2733926397328841</v>
+        <v>-0.3840772448438993</v>
       </c>
       <c r="E4">
-        <v>0.7845514100021342</v>
+        <v>0.700921196448353</v>
       </c>
       <c r="F4">
-        <v>0.9151839491412127</v>
+        <v>0.9082528607820531</v>
       </c>
       <c r="G4">
-        <v>1.069221870557057</v>
+        <v>1.066835277816666</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.9879804594598375</v>
+        <v>0.9685191865001239</v>
       </c>
       <c r="C5">
-        <v>0.04138455759315535</v>
+        <v>0.04298965472476757</v>
       </c>
       <c r="D5">
-        <v>-0.2921949637202916</v>
+        <v>-0.7440624030182265</v>
       </c>
       <c r="E5">
-        <v>0.7701375620685283</v>
+        <v>0.456838723383521</v>
       </c>
       <c r="F5">
-        <v>0.9110070876248419</v>
+        <v>0.8902569404663166</v>
       </c>
       <c r="G5">
-        <v>1.071457512827208</v>
+        <v>1.053661445343545</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="6">
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.217700818172391</v>
+        <v>1.249690321259002</v>
       </c>
       <c r="C9">
-        <v>0.2484914120313861</v>
+        <v>0.2536471078782603</v>
       </c>
       <c r="D9">
-        <v>0.7926410970111315</v>
+        <v>0.8787633318296169</v>
       </c>
       <c r="E9">
-        <v>0.4279869574849779</v>
+        <v>0.37952961175553</v>
       </c>
       <c r="F9">
-        <v>0.7482114059840357</v>
+        <v>0.7601470188185637</v>
       </c>
       <c r="G9">
-        <v>1.9817865254641</v>
+        <v>2.05450506334379</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9724479349606511</v>
+        <v>0.9229065790376197</v>
       </c>
       <c r="C10">
-        <v>0.2483674270333009</v>
+        <v>0.2573624753725321</v>
       </c>
       <c r="D10">
-        <v>-0.1124895586025813</v>
+        <v>-0.3117286774725227</v>
       </c>
       <c r="E10">
-        <v>0.9104352482248051</v>
+        <v>0.7552467317141522</v>
       </c>
       <c r="F10">
-        <v>0.5976619689586263</v>
+        <v>0.5573017486014193</v>
       </c>
       <c r="G10">
-        <v>1.582257254643382</v>
+        <v>1.528357942117451</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9010786573023761</v>
+        <v>0.8253100827823208</v>
       </c>
       <c r="C11">
-        <v>0.2569205558796471</v>
+        <v>0.2652126493636578</v>
       </c>
       <c r="D11">
-        <v>-0.4054277588842671</v>
+        <v>-0.723932684987136</v>
       </c>
       <c r="E11">
-        <v>0.6851631099648255</v>
+        <v>0.469107062579142</v>
       </c>
       <c r="F11">
-        <v>0.5445923414250731</v>
+        <v>0.4907583916425196</v>
       </c>
       <c r="G11">
-        <v>1.490918407925431</v>
+        <v>1.387926817639255</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="O11">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="12">
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.2121418857558</v>
+        <v>1.238336467124876</v>
       </c>
       <c r="C15">
-        <v>0.2295749758187715</v>
+        <v>0.2341902509968719</v>
       </c>
       <c r="D15">
-        <v>0.8380222956112451</v>
+        <v>0.9128002521075275</v>
       </c>
       <c r="E15">
-        <v>0.4020181817483137</v>
+        <v>0.3613476057161299</v>
       </c>
       <c r="F15">
-        <v>0.7729277234644389</v>
+        <v>0.7825202038119238</v>
       </c>
       <c r="G15">
-        <v>1.900938349860114</v>
+        <v>1.959664681296696</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9406053138918308</v>
+        <v>0.9097374725838165</v>
       </c>
       <c r="C16">
-        <v>0.2310865856658182</v>
+        <v>0.2393928092641172</v>
       </c>
       <c r="D16">
-        <v>-0.2649728016031444</v>
+        <v>-0.3951631339717206</v>
       </c>
       <c r="E16">
-        <v>0.7910304143109627</v>
+        <v>0.6927224980656683</v>
       </c>
       <c r="F16">
-        <v>0.5980068649594423</v>
+        <v>0.5690423054601231</v>
       </c>
       <c r="G16">
-        <v>1.479478595252504</v>
+        <v>1.454412547330697</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9344700014862403</v>
+        <v>0.8428991454276602</v>
       </c>
       <c r="C17">
-        <v>0.2407587712122368</v>
+        <v>0.2503472810790322</v>
       </c>
       <c r="D17">
-        <v>-0.2815089701564608</v>
+        <v>-0.682683531015043</v>
       </c>
       <c r="E17">
-        <v>0.7783200489708443</v>
+        <v>0.4948068385542627</v>
       </c>
       <c r="F17">
-        <v>0.5829497582650502</v>
+        <v>0.5160355500802098</v>
       </c>
       <c r="G17">
-        <v>1.497957879383252</v>
+        <v>1.37680237195334</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="O17">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="18">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.009545917456051</v>
+        <v>1.011063772171523</v>
       </c>
       <c r="C21">
-        <v>0.02232151765466691</v>
+        <v>0.02267617667469851</v>
       </c>
       <c r="D21">
-        <v>0.4256271114080233</v>
+        <v>0.4852236122930644</v>
       </c>
       <c r="E21">
-        <v>0.6703795816665585</v>
+        <v>0.6275177343603568</v>
       </c>
       <c r="F21">
-        <v>0.9663311215213649</v>
+        <v>0.9671115114876981</v>
       </c>
       <c r="G21">
-        <v>1.054693300002184</v>
+        <v>1.057013528693493</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.9862623272864895</v>
+        <v>0.9816848063240543</v>
       </c>
       <c r="C22">
-        <v>0.02260070744563526</v>
+        <v>0.0233836474759364</v>
       </c>
       <c r="D22">
-        <v>-0.6120564050325304</v>
+        <v>-0.7905094072996086</v>
       </c>
       <c r="E22">
-        <v>0.5405004394888028</v>
+        <v>0.429230330479762</v>
       </c>
       <c r="F22">
-        <v>0.9435277712033379</v>
+        <v>0.9377085428327092</v>
       </c>
       <c r="G22">
-        <v>1.030932430302505</v>
+        <v>1.027723450248469</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9713239031458514</v>
+        <v>0.9583392058980079</v>
       </c>
       <c r="C23">
-        <v>0.02428961801572502</v>
+        <v>0.02562274262964875</v>
       </c>
       <c r="D23">
-        <v>-1.197848785482712</v>
+        <v>-1.66077016653003</v>
       </c>
       <c r="E23">
-        <v>0.2309758908147051</v>
+        <v>0.09675961503921145</v>
       </c>
       <c r="F23">
-        <v>0.9261657488185793</v>
+        <v>0.9114002377561345</v>
       </c>
       <c r="G23">
-        <v>1.018683886794546</v>
+        <v>1.007695626481685</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="24">
@@ -2013,22 +2013,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.221174268189071</v>
+        <v>1.249164898539687</v>
       </c>
       <c r="C27">
-        <v>0.2308347471997717</v>
+        <v>0.2354162895814158</v>
       </c>
       <c r="D27">
-        <v>0.8656101958552259</v>
+        <v>0.9450291110945004</v>
       </c>
       <c r="E27">
-        <v>0.3867039623941836</v>
+        <v>0.344644014113008</v>
       </c>
       <c r="F27">
-        <v>0.7767669726007681</v>
+        <v>0.7874682692788776</v>
       </c>
       <c r="G27">
-        <v>1.919837796777146</v>
+        <v>1.981556596778957</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9394999558434942</v>
+        <v>0.8819631129696054</v>
       </c>
       <c r="C28">
-        <v>0.2321068005109007</v>
+        <v>0.2408075066928357</v>
       </c>
       <c r="D28">
-        <v>-0.268874100161031</v>
+        <v>-0.5215993787106222</v>
       </c>
       <c r="E28">
-        <v>0.7880265683478502</v>
+        <v>0.6019492959819948</v>
       </c>
       <c r="F28">
-        <v>0.5961109469163489</v>
+        <v>0.5501418712975652</v>
       </c>
       <c r="G28">
-        <v>1.480697798951492</v>
+        <v>1.41392424976557</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.8107675955877979</v>
+        <v>0.7420987013993746</v>
       </c>
       <c r="C29">
-        <v>0.2433943645117212</v>
+        <v>0.2521275856659159</v>
       </c>
       <c r="D29">
-        <v>-0.8618680699464033</v>
+        <v>-1.1830241546936</v>
       </c>
       <c r="E29">
-        <v>0.3887601214966744</v>
+        <v>0.2367995745884725</v>
       </c>
       <c r="F29">
-        <v>0.5031746161805407</v>
+        <v>0.4527414752038849</v>
       </c>
       <c r="G29">
-        <v>1.306393591642075</v>
+        <v>1.216390617560793</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="O29">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="30">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.092397587757216</v>
+        <v>1.106121055424533</v>
       </c>
       <c r="C33">
-        <v>0.1539903549893032</v>
+        <v>0.1567932947624241</v>
       </c>
       <c r="D33">
-        <v>0.5738989459206149</v>
+        <v>0.6432631614187008</v>
       </c>
       <c r="E33">
-        <v>0.5660361864077919</v>
+        <v>0.5200533555803856</v>
       </c>
       <c r="F33">
-        <v>0.8078001038164876</v>
+        <v>0.8134670474496538</v>
       </c>
       <c r="G33">
-        <v>1.477262114847264</v>
+        <v>1.504060666119616</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2454,22 +2454,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.9222956286581114</v>
+        <v>0.8857138600818709</v>
       </c>
       <c r="C34">
-        <v>0.1556770215831106</v>
+        <v>0.1617700919654306</v>
       </c>
       <c r="D34">
-        <v>-0.5195979955080422</v>
+        <v>-0.7502087442902827</v>
       </c>
       <c r="E34">
-        <v>0.6033437954854128</v>
+        <v>0.4531289931563925</v>
       </c>
       <c r="F34">
-        <v>0.679763167962411</v>
+        <v>0.6450516476055248</v>
       </c>
       <c r="G34">
-        <v>1.251361160375342</v>
+        <v>1.216164697591587</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2517,22 +2517,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.8303223903727338</v>
+        <v>0.7738990391409071</v>
       </c>
       <c r="C35">
-        <v>0.1675465938772056</v>
+        <v>0.1757099832742863</v>
       </c>
       <c r="D35">
-        <v>-1.109788191864377</v>
+        <v>-1.458732449406769</v>
       </c>
       <c r="E35">
-        <v>0.2670903087980466</v>
+        <v>0.1446387612152218</v>
       </c>
       <c r="F35">
-        <v>0.5979031341351885</v>
+        <v>0.5484280996749015</v>
       </c>
       <c r="G35">
-        <v>1.153088573371496</v>
+        <v>1.092066076005676</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="O35">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="36">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.9905284866208233</v>
+        <v>1.007132993899727</v>
       </c>
       <c r="C39">
-        <v>0.08810101059047444</v>
+        <v>0.08966733968196124</v>
       </c>
       <c r="D39">
-        <v>-0.1080197985699391</v>
+        <v>0.07926714961175993</v>
       </c>
       <c r="E39">
-        <v>0.9139799871139026</v>
+        <v>0.9368201348709552</v>
       </c>
       <c r="F39">
-        <v>0.8334417534000447</v>
+        <v>0.8448154465436847</v>
       </c>
       <c r="G39">
-        <v>1.177222857871865</v>
+        <v>1.200637217928731</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.049296829286749</v>
+        <v>1.065405910930919</v>
       </c>
       <c r="C40">
-        <v>0.09446454085231049</v>
+        <v>0.09531879981979408</v>
       </c>
       <c r="D40">
-        <v>0.509400172822482</v>
+        <v>0.6646733245827495</v>
       </c>
       <c r="E40">
-        <v>0.6104717552306174</v>
+        <v>0.5062594591298135</v>
       </c>
       <c r="F40">
-        <v>0.871946818884386</v>
+        <v>0.883852088429824</v>
       </c>
       <c r="G40">
-        <v>1.262719023804609</v>
+        <v>1.284253066667574</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.122658368747208</v>
+        <v>1.03275693117441</v>
       </c>
       <c r="C41">
-        <v>0.09270909242476723</v>
+        <v>0.09520213727958086</v>
       </c>
       <c r="D41">
-        <v>1.247983486842128</v>
+        <v>0.3385623429270225</v>
       </c>
       <c r="E41">
-        <v>0.2120371045702443</v>
+        <v>0.7349394548304604</v>
       </c>
       <c r="F41">
-        <v>0.9361242498336272</v>
+        <v>0.8569626859304057</v>
       </c>
       <c r="G41">
-        <v>1.346361674897473</v>
+        <v>1.244612976037329</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="42">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.8377943558720645</v>
+        <v>0.9672979622095348</v>
       </c>
       <c r="C45">
-        <v>0.5715844261251661</v>
+        <v>0.5795425336411215</v>
       </c>
       <c r="D45">
-        <v>-0.3096351111868431</v>
+        <v>-0.05737059584880784</v>
       </c>
       <c r="E45">
-        <v>0.7568384527307154</v>
+        <v>0.9542499855243201</v>
       </c>
       <c r="F45">
-        <v>0.2732775054341193</v>
+        <v>0.3106367071210994</v>
       </c>
       <c r="G45">
-        <v>2.568449172631586</v>
+        <v>3.012088804205475</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.78814159879579</v>
+        <v>1.599527700188325</v>
       </c>
       <c r="C46">
-        <v>0.6024289155024424</v>
+        <v>0.5934328733762894</v>
       </c>
       <c r="D46">
-        <v>0.9647227293004448</v>
+        <v>0.7915105808255936</v>
       </c>
       <c r="E46">
-        <v>0.3346837076095431</v>
+        <v>0.4286461042174309</v>
       </c>
       <c r="F46">
-        <v>0.5490520078142545</v>
+        <v>0.499874275702933</v>
       </c>
       <c r="G46">
-        <v>5.82358379868755</v>
+        <v>5.118264707804688</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3273,22 +3273,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.64282155409475</v>
+        <v>1.217190106519318</v>
       </c>
       <c r="C47">
-        <v>0.5717910337141412</v>
+        <v>0.5873462149513781</v>
       </c>
       <c r="D47">
-        <v>0.8681759490522053</v>
+        <v>0.3346322934233027</v>
       </c>
       <c r="E47">
-        <v>0.3852980185404978</v>
+        <v>0.7379024813582894</v>
       </c>
       <c r="F47">
-        <v>0.5356498429823897</v>
+        <v>0.3849536210261595</v>
       </c>
       <c r="G47">
-        <v>5.038483057460764</v>
+        <v>3.848650004795852</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="O47">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="48">
@@ -3525,22 +3525,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.9187060766212125</v>
+        <v>1.013624631708006</v>
       </c>
       <c r="C51">
-        <v>0.5048940820937791</v>
+        <v>0.515721548319623</v>
       </c>
       <c r="D51">
-        <v>-0.1679343061529364</v>
+        <v>0.02624022786161461</v>
       </c>
       <c r="E51">
-        <v>0.8666349609690385</v>
+        <v>0.9790657297252577</v>
       </c>
       <c r="F51">
-        <v>0.3415151443933438</v>
+        <v>0.3688877027622088</v>
       </c>
       <c r="G51">
-        <v>2.471400958572516</v>
+        <v>2.78522402972997</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>1.370369589692022</v>
+        <v>1.430851957766425</v>
       </c>
       <c r="C52">
-        <v>0.5370253096480497</v>
+        <v>0.5418721734805328</v>
       </c>
       <c r="D52">
-        <v>0.5867143899828988</v>
+        <v>0.6611707687980343</v>
       </c>
       <c r="E52">
-        <v>0.5573955416461622</v>
+        <v>0.508502805052913</v>
       </c>
       <c r="F52">
-        <v>0.4783226430449987</v>
+        <v>0.4947118027095093</v>
       </c>
       <c r="G52">
-        <v>3.926037873511278</v>
+        <v>4.138444471772973</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="B53">
-        <v>1.822632874741338</v>
+        <v>1.23488498608616</v>
       </c>
       <c r="C53">
-        <v>0.5214104134437214</v>
+        <v>0.5388682764466449</v>
       </c>
       <c r="D53">
-        <v>1.151266017549846</v>
+        <v>0.3915202402695375</v>
       </c>
       <c r="E53">
-        <v>0.2496228129545475</v>
+        <v>0.6954127307173814</v>
       </c>
       <c r="F53">
-        <v>0.6559547039232871</v>
+        <v>0.4294780790423121</v>
       </c>
       <c r="G53">
-        <v>5.064359743468467</v>
+        <v>3.550683965667031</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="O53">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="54">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.9789802188707213</v>
+        <v>0.9841665029040498</v>
       </c>
       <c r="C57">
-        <v>0.03958725815966261</v>
+        <v>0.03990541684777376</v>
       </c>
       <c r="D57">
-        <v>-0.5366333281702239</v>
+        <v>-0.3999503635525455</v>
       </c>
       <c r="E57">
-        <v>0.5915209179221645</v>
+        <v>0.6891930763852097</v>
       </c>
       <c r="F57">
-        <v>0.9058935789744889</v>
+        <v>0.9101249640333028</v>
       </c>
       <c r="G57">
-        <v>1.057963419969395</v>
+        <v>1.064231554693346</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.9968187909901653</v>
+        <v>0.9963877314704563</v>
       </c>
       <c r="C58">
-        <v>0.04050487677134514</v>
+        <v>0.04129227760435736</v>
       </c>
       <c r="D58">
-        <v>-0.07866410334359954</v>
+        <v>-0.08763886943737513</v>
       </c>
       <c r="E58">
-        <v>0.9372997983491584</v>
+        <v>0.9301637076757053</v>
       </c>
       <c r="F58">
-        <v>0.9207429509257757</v>
+        <v>0.9189255375097054</v>
       </c>
       <c r="G58">
-        <v>1.079180352205809</v>
+        <v>1.080379716201278</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.9791282315454566</v>
+        <v>0.9430306644209608</v>
       </c>
       <c r="C59">
-        <v>0.04235668258278973</v>
+        <v>0.04550703818982135</v>
       </c>
       <c r="D59">
-        <v>-0.497977215679397</v>
+        <v>-1.288954000674591</v>
       </c>
       <c r="E59">
-        <v>0.6185001014336169</v>
+        <v>0.1974140788335499</v>
       </c>
       <c r="F59">
-        <v>0.9011259561234529</v>
+        <v>0.8625616668556982</v>
       </c>
       <c r="G59">
-        <v>1.063882454272568</v>
+        <v>1.031006672578014</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="60">
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>0.9846781544064667</v>
+        <v>1.096569248797687</v>
       </c>
       <c r="C63">
-        <v>0.4884655192315217</v>
+        <v>0.493076252186289</v>
       </c>
       <c r="D63">
-        <v>-0.03161008789969542</v>
+        <v>0.186961835763036</v>
       </c>
       <c r="E63">
-        <v>0.974782998430609</v>
+        <v>0.8516905559204948</v>
       </c>
       <c r="F63">
-        <v>0.3780173203493334</v>
+        <v>0.4171851067341166</v>
       </c>
       <c r="G63">
-        <v>2.56493820671843</v>
+        <v>2.882327527993676</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>1.349428483146366</v>
+        <v>1.193911927021626</v>
       </c>
       <c r="C64">
-        <v>0.5061881455515381</v>
+        <v>0.5070726573739291</v>
       </c>
       <c r="D64">
-        <v>0.5920351150660829</v>
+        <v>0.3495263385018788</v>
       </c>
       <c r="E64">
-        <v>0.5538270743815599</v>
+        <v>0.7266942009123439</v>
       </c>
       <c r="F64">
-        <v>0.5003590302783194</v>
+        <v>0.4419277389927296</v>
       </c>
       <c r="G64">
-        <v>3.639301223591018</v>
+        <v>3.225472319826351</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4407,22 +4407,22 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.9952885829849537</v>
+        <v>0.754465894822027</v>
       </c>
       <c r="C65">
-        <v>0.4988432481281009</v>
+        <v>0.5197315295211148</v>
       </c>
       <c r="D65">
-        <v>-0.009467003396441524</v>
+        <v>-0.5420975795176117</v>
       </c>
       <c r="E65">
-        <v>0.9924465369818675</v>
+        <v>0.5877512860855385</v>
       </c>
       <c r="F65">
-        <v>0.3743974478707846</v>
+        <v>0.2724227248454398</v>
       </c>
       <c r="G65">
-        <v>2.645849668724455</v>
+        <v>2.089468809081734</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="O65">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="66">
@@ -4659,22 +4659,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.8723923657395393</v>
+        <v>0.9123351928315033</v>
       </c>
       <c r="C69">
-        <v>0.2898583939976335</v>
+        <v>0.2932954208099355</v>
       </c>
       <c r="D69">
-        <v>-0.4709747876604701</v>
+        <v>-0.3128170913129134</v>
       </c>
       <c r="E69">
-        <v>0.6376587395094623</v>
+        <v>0.754419629611622</v>
       </c>
       <c r="F69">
-        <v>0.4942924126780923</v>
+        <v>0.5134532569708753</v>
       </c>
       <c r="G69">
-        <v>1.539712972078888</v>
+        <v>1.621093045527434</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4722,22 +4722,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>1.016193821488821</v>
+        <v>0.9808390147257477</v>
       </c>
       <c r="C70">
-        <v>0.2933702170457821</v>
+        <v>0.3005719288564035</v>
       </c>
       <c r="D70">
-        <v>0.05475709261096108</v>
+        <v>-0.06436707576959819</v>
       </c>
       <c r="E70">
-        <v>0.9563319842214157</v>
+        <v>0.9486779453728336</v>
       </c>
       <c r="F70">
-        <v>0.5718200360466649</v>
+        <v>0.5441898568551008</v>
       </c>
       <c r="G70">
-        <v>1.80590013944139</v>
+        <v>1.767848409317808</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.8697655896594173</v>
+        <v>0.706855248922622</v>
       </c>
       <c r="C71">
-        <v>0.3046818239037608</v>
+        <v>0.3275667563472041</v>
       </c>
       <c r="D71">
-        <v>-0.4579582038191464</v>
+        <v>-1.05911044750448</v>
       </c>
       <c r="E71">
-        <v>0.6469824695953353</v>
+        <v>0.2895494824902091</v>
       </c>
       <c r="F71">
-        <v>0.4786924558321871</v>
+        <v>0.3719676395776237</v>
       </c>
       <c r="G71">
-        <v>1.580330276232291</v>
+        <v>1.343246803665011</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="O71">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="72">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.9281233037033972</v>
+        <v>0.9152407736122009</v>
       </c>
       <c r="C74">
-        <v>0.07797189466492592</v>
+        <v>0.08129897530142657</v>
       </c>
       <c r="D74">
-        <v>-0.9566355283904018</v>
+        <v>-1.08941235032619</v>
       </c>
       <c r="E74">
-        <v>0.3387512497500082</v>
+        <v>0.2759720875543029</v>
       </c>
       <c r="F74">
-        <v>0.7965918892453846</v>
+        <v>0.7804292646903591</v>
       </c>
       <c r="G74">
-        <v>1.081372881781823</v>
+        <v>1.073339649833108</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>1.118333908873153</v>
+        <v>1.072475191835682</v>
       </c>
       <c r="C75">
-        <v>0.07662451003785084</v>
+        <v>0.07741763133317968</v>
       </c>
       <c r="D75">
-        <v>1.459585142415003</v>
+        <v>0.9037894752403388</v>
       </c>
       <c r="E75">
-        <v>0.1444041250522103</v>
+        <v>0.3661070435840626</v>
       </c>
       <c r="F75">
-        <v>0.9623844388016201</v>
+        <v>0.9214870742910543</v>
       </c>
       <c r="G75">
-        <v>1.299554191974327</v>
+        <v>1.248203115586717</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.9080817412849147</v>
+        <v>0.9110368223782751</v>
       </c>
       <c r="C76">
-        <v>0.08041675977384098</v>
+        <v>0.08304038142014902</v>
       </c>
       <c r="D76">
-        <v>-1.199014748447246</v>
+        <v>-1.122007885933999</v>
       </c>
       <c r="E76">
-        <v>0.2305222108955075</v>
+        <v>0.261859086945209</v>
       </c>
       <c r="F76">
-        <v>0.7756647821454019</v>
+        <v>0.7741976163876155</v>
       </c>
       <c r="G76">
-        <v>1.063104149932213</v>
+        <v>1.072062318664589</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>1.075115659430974</v>
+        <v>1.032996187352277</v>
       </c>
       <c r="C77">
-        <v>0.07701757320564699</v>
+        <v>0.08048604671865962</v>
       </c>
       <c r="D77">
-        <v>0.940411946857562</v>
+        <v>0.4033431955539241</v>
       </c>
       <c r="E77">
-        <v>0.347006296502196</v>
+        <v>0.6866957688924146</v>
       </c>
       <c r="F77">
-        <v>0.9244804049270332</v>
+        <v>0.8822443208702025</v>
       </c>
       <c r="G77">
-        <v>1.250295490302933</v>
+        <v>1.209507500180702</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="O77">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="78">
@@ -5226,22 +5226,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.8670690411067715</v>
+        <v>0.6912593531802701</v>
       </c>
       <c r="C78">
-        <v>0.5637080304678509</v>
+        <v>0.5670514591574007</v>
       </c>
       <c r="D78">
-        <v>-0.2530328919847866</v>
+        <v>-0.6511581787734599</v>
       </c>
       <c r="E78">
-        <v>0.8002427959239697</v>
+        <v>0.5149443838436996</v>
       </c>
       <c r="F78">
-        <v>0.2872265187192384</v>
+        <v>0.2274919029290564</v>
       </c>
       <c r="G78">
-        <v>2.61747670583545</v>
+        <v>2.100468136258108</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5279,7 +5279,7 @@
         </is>
       </c>
       <c r="O78">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="79">
@@ -5289,22 +5289,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>1.595867411930289</v>
+        <v>1.363297324460637</v>
       </c>
       <c r="C79">
-        <v>0.5147922503359704</v>
+        <v>0.5446653498050006</v>
       </c>
       <c r="D79">
-        <v>0.9079729153653311</v>
+        <v>0.5689847330524677</v>
       </c>
       <c r="E79">
-        <v>0.3638925316110334</v>
+        <v>0.5693665006734822</v>
       </c>
       <c r="F79">
-        <v>0.5818417067149697</v>
+        <v>0.4687816422153676</v>
       </c>
       <c r="G79">
-        <v>4.377123136875253</v>
+        <v>3.964702171565976</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="O79">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="80">
@@ -5352,22 +5352,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.7938220472163672</v>
+        <v>0.6690319201216476</v>
       </c>
       <c r="C80">
-        <v>0.5394038168284446</v>
+        <v>0.5985140040761358</v>
       </c>
       <c r="D80">
-        <v>-0.4280577139876743</v>
+        <v>-0.6715356768071533</v>
       </c>
       <c r="E80">
-        <v>0.6686091021464993</v>
+        <v>0.5018793395649661</v>
       </c>
       <c r="F80">
-        <v>0.2757920832106234</v>
+        <v>0.2070097471720024</v>
       </c>
       <c r="G80">
-        <v>2.284885901403972</v>
+        <v>2.162234949109663</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="O80">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="81">
@@ -5415,22 +5415,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>1.330134851925916</v>
+        <v>1.089073158273205</v>
       </c>
       <c r="C81">
-        <v>0.5618925337917375</v>
+        <v>0.5572468583313558</v>
       </c>
       <c r="D81">
-        <v>0.5077133301526239</v>
+        <v>0.1531224801592226</v>
       </c>
       <c r="E81">
-        <v>0.6116543986437348</v>
+        <v>0.8783016883222876</v>
       </c>
       <c r="F81">
-        <v>0.4421930180108871</v>
+        <v>0.3653656113466367</v>
       </c>
       <c r="G81">
-        <v>4.001100542624169</v>
+        <v>3.246283468495048</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="O81">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="82">
@@ -5478,22 +5478,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.732566367861855</v>
+        <v>0.6314649620836852</v>
       </c>
       <c r="C82">
-        <v>0.4703759297350442</v>
+        <v>0.4740444371122122</v>
       </c>
       <c r="D82">
-        <v>-0.6616013233946612</v>
+        <v>-0.9697673601395553</v>
       </c>
       <c r="E82">
-        <v>0.5082267591879581</v>
+        <v>0.3321624657834524</v>
       </c>
       <c r="F82">
-        <v>0.2913816907884516</v>
+        <v>0.2493686772167722</v>
       </c>
       <c r="G82">
-        <v>1.841754304706575</v>
+        <v>1.599030009662058</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="O82">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="83">
@@ -5541,22 +5541,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.697034269716145</v>
+        <v>1.401297019146976</v>
       </c>
       <c r="C83">
-        <v>0.4334433314681663</v>
+        <v>0.4528549285581959</v>
       </c>
       <c r="D83">
-        <v>1.220187604571729</v>
+        <v>0.7450470972249665</v>
       </c>
       <c r="E83">
-        <v>0.2223937647081647</v>
+        <v>0.4562432486943808</v>
       </c>
       <c r="F83">
-        <v>0.7256763672553883</v>
+        <v>0.5768453341097405</v>
       </c>
       <c r="G83">
-        <v>3.968608380459318</v>
+        <v>3.404089830943549</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="O83">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="84">
@@ -5604,22 +5604,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.6584678152489555</v>
+        <v>0.6093824997688372</v>
       </c>
       <c r="C84">
-        <v>0.4587188441987012</v>
+        <v>0.4970194437353593</v>
       </c>
       <c r="D84">
-        <v>-0.910883954590868</v>
+        <v>-0.996558859489059</v>
       </c>
       <c r="E84">
-        <v>0.3623565207791214</v>
+        <v>0.3189786836662203</v>
       </c>
       <c r="F84">
-        <v>0.2679614777589159</v>
+        <v>0.2300521309746205</v>
       </c>
       <c r="G84">
-        <v>1.618067892985808</v>
+        <v>1.614186443095735</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="O84">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="85">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.395554857945649</v>
+        <v>1.138263033284157</v>
       </c>
       <c r="C85">
-        <v>0.4690756860504906</v>
+        <v>0.4734571761168234</v>
       </c>
       <c r="D85">
-        <v>0.7105294385011528</v>
+        <v>0.2735272628285922</v>
       </c>
       <c r="E85">
-        <v>0.4773758821897937</v>
+        <v>0.7844479383725951</v>
       </c>
       <c r="F85">
-        <v>0.5565048646149011</v>
+        <v>0.4500234583268631</v>
       </c>
       <c r="G85">
-        <v>3.499651998340414</v>
+        <v>2.879055989121778</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.9352565899812345</v>
+        <v>0.9462346870503089</v>
       </c>
       <c r="C86">
-        <v>0.03972594405893456</v>
+        <v>0.04380865152238504</v>
       </c>
       <c r="D86">
-        <v>-1.684902930315566</v>
+        <v>-1.261500987013128</v>
       </c>
       <c r="E86">
-        <v>0.09200730113629049</v>
+        <v>0.2071284046013198</v>
       </c>
       <c r="F86">
-        <v>0.8651989667280916</v>
+        <v>0.8683781206316556</v>
       </c>
       <c r="G86">
-        <v>1.010986978418599</v>
+        <v>1.031071674544165</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>1.042931323347234</v>
+        <v>1.022261522912449</v>
       </c>
       <c r="C87">
-        <v>0.04316818050452158</v>
+        <v>0.04228037167916461</v>
       </c>
       <c r="D87">
-        <v>0.9737572456098792</v>
+        <v>0.5207464228130169</v>
       </c>
       <c r="E87">
-        <v>0.3301770861437909</v>
+        <v>0.602543430569801</v>
       </c>
       <c r="F87">
-        <v>0.9583207446514874</v>
+        <v>0.94096375898603</v>
       </c>
       <c r="G87">
-        <v>1.135012208897116</v>
+        <v>1.110583283625479</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.9379290758503775</v>
+        <v>0.9474595819255597</v>
       </c>
       <c r="C88">
-        <v>0.0451417503728561</v>
+        <v>0.043600974516405</v>
       </c>
       <c r="D88">
-        <v>-1.419549406152273</v>
+        <v>-1.237839317409384</v>
       </c>
       <c r="E88">
-        <v>0.1557389036280055</v>
+        <v>0.2157756466116489</v>
       </c>
       <c r="F88">
-        <v>0.858509828834108</v>
+        <v>0.8698562244207928</v>
       </c>
       <c r="G88">
-        <v>1.024695258900212</v>
+        <v>1.031986245750314</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.002926172612638</v>
+        <v>0.9873807654639556</v>
       </c>
       <c r="C89">
-        <v>0.04031137827457667</v>
+        <v>0.04507801265637232</v>
       </c>
       <c r="D89">
-        <v>0.07248324984427933</v>
+        <v>-0.2817234519134783</v>
       </c>
       <c r="E89">
-        <v>0.9422173350913797</v>
+        <v>0.7781555705327313</v>
       </c>
       <c r="F89">
-        <v>0.9267356235027051</v>
+        <v>0.9038871010283853</v>
       </c>
       <c r="G89">
-        <v>1.08538064384497</v>
+        <v>1.078586888671145</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="O89">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="90">
@@ -5982,22 +5982,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.7375198192726917</v>
+        <v>0.6938222535696252</v>
       </c>
       <c r="C90">
-        <v>0.4298940703946514</v>
+        <v>0.4559926447097072</v>
       </c>
       <c r="D90">
-        <v>-0.7082263713469172</v>
+        <v>-0.8016345752414765</v>
       </c>
       <c r="E90">
-        <v>0.4788046920203993</v>
+        <v>0.422764371245378</v>
       </c>
       <c r="F90">
-        <v>0.3175756527419787</v>
+        <v>0.2838615581713497</v>
       </c>
       <c r="G90">
-        <v>1.712774512540973</v>
+        <v>1.695859498022794</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="O90">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="91">
@@ -6045,22 +6045,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>1.277711455137242</v>
+        <v>1.138513197816551</v>
       </c>
       <c r="C91">
-        <v>0.4391831313770039</v>
+        <v>0.4464935974071644</v>
       </c>
       <c r="D91">
-        <v>0.5580144921374839</v>
+        <v>0.2905376459883242</v>
       </c>
       <c r="E91">
-        <v>0.5768344881877357</v>
+        <v>0.7714049548371655</v>
       </c>
       <c r="F91">
-        <v>0.5402557890741538</v>
+        <v>0.4745500573728154</v>
       </c>
       <c r="G91">
-        <v>3.02180299703341</v>
+        <v>2.731455368014295</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="O91">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="92">
@@ -6108,22 +6108,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.7165186330563007</v>
+        <v>0.6492269102075132</v>
       </c>
       <c r="C92">
-        <v>0.4569745811273876</v>
+        <v>0.4749846689710133</v>
       </c>
       <c r="D92">
-        <v>-0.729473892329812</v>
+        <v>-0.9094461802321144</v>
       </c>
       <c r="E92">
-        <v>0.4657118321980405</v>
+        <v>0.3631146546800404</v>
       </c>
       <c r="F92">
-        <v>0.2925836274824186</v>
+        <v>0.2559109267947879</v>
       </c>
       <c r="G92">
-        <v>1.75470840912901</v>
+        <v>1.647040187836868</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="O92">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="93">
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.9523209357239754</v>
+        <v>0.8484039668977275</v>
       </c>
       <c r="C93">
-        <v>0.4435502350394491</v>
+        <v>0.4638994184531114</v>
       </c>
       <c r="D93">
-        <v>-0.1101412642484527</v>
+        <v>-0.3543836746138578</v>
       </c>
       <c r="E93">
-        <v>0.9122973430757206</v>
+        <v>0.7230513675129711</v>
       </c>
       <c r="F93">
-        <v>0.3992387501840157</v>
+        <v>0.3417675220394304</v>
       </c>
       <c r="G93">
-        <v>2.27161107031864</v>
+        <v>2.106078678139454</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="O93">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="94">
@@ -6234,22 +6234,22 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.6554197066043127</v>
+        <v>0.6677994750882643</v>
       </c>
       <c r="C94">
-        <v>0.2586091264741373</v>
+        <v>0.2797581345263678</v>
       </c>
       <c r="D94">
-        <v>-1.633660346302908</v>
+        <v>-1.443272912109678</v>
       </c>
       <c r="E94">
-        <v>0.1023301889926183</v>
+        <v>0.1489436072757182</v>
       </c>
       <c r="F94">
-        <v>0.3948126031438763</v>
+        <v>0.3859362010012852</v>
       </c>
       <c r="G94">
-        <v>1.088047819103533</v>
+        <v>1.155517771515495</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="O94">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="95">
@@ -6297,22 +6297,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.19318612759113</v>
+        <v>1.127207022957209</v>
       </c>
       <c r="C95">
-        <v>0.2693176586362047</v>
+        <v>0.2690932622330735</v>
       </c>
       <c r="D95">
-        <v>0.6558320321906815</v>
+        <v>0.4449866601411199</v>
       </c>
       <c r="E95">
-        <v>0.5119322038297898</v>
+        <v>0.6563293944574522</v>
       </c>
       <c r="F95">
-        <v>0.7038248376354531</v>
+        <v>0.6651982313896927</v>
       </c>
       <c r="G95">
-        <v>2.022794676952451</v>
+        <v>1.910100797997615</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         </is>
       </c>
       <c r="O95">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="96">
@@ -6360,22 +6360,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.677038235133029</v>
+        <v>0.6594148820463115</v>
       </c>
       <c r="C96">
-        <v>0.283822232457067</v>
+        <v>0.2850298539205739</v>
       </c>
       <c r="D96">
-        <v>-1.374196541922666</v>
+        <v>-1.460907949813785</v>
       </c>
       <c r="E96">
-        <v>0.1693806740327085</v>
+        <v>0.1440407046428769</v>
       </c>
       <c r="F96">
-        <v>0.3881711672271154</v>
+        <v>0.3771732576539688</v>
       </c>
       <c r="G96">
-        <v>1.180872796674906</v>
+        <v>1.152860065872105</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="O96">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="97">
@@ -6423,22 +6423,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.9210415929275986</v>
+        <v>0.9037458317932144</v>
       </c>
       <c r="C97">
-        <v>0.2666658390252565</v>
+        <v>0.2896199388438341</v>
       </c>
       <c r="D97">
-        <v>-0.308438769026073</v>
+        <v>-0.3494480319535635</v>
       </c>
       <c r="E97">
-        <v>0.7577484855458392</v>
+        <v>0.7267529790061643</v>
       </c>
       <c r="F97">
-        <v>0.5461260202627346</v>
+        <v>0.5122964759285378</v>
       </c>
       <c r="G97">
-        <v>1.55333674724836</v>
+        <v>1.59430440547778</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>1.015025239487568</v>
+        <v>0.8958670724851183</v>
       </c>
       <c r="C98">
-        <v>0.1603551309057271</v>
+        <v>0.1628995615787135</v>
       </c>
       <c r="D98">
-        <v>0.09300281562905957</v>
+        <v>-0.6750370139052314</v>
       </c>
       <c r="E98">
-        <v>0.9259013243711767</v>
+        <v>0.4996522490311857</v>
       </c>
       <c r="F98">
-        <v>0.7412800405310915</v>
+        <v>0.6510033392267144</v>
       </c>
       <c r="G98">
-        <v>1.389861024800628</v>
+        <v>1.232832096554816</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>1.107897615327464</v>
+        <v>1.030169564369495</v>
       </c>
       <c r="C99">
-        <v>0.1192985681037771</v>
+        <v>0.1406099062490203</v>
       </c>
       <c r="D99">
-        <v>0.858888591414171</v>
+        <v>0.2113891907519569</v>
       </c>
       <c r="E99">
-        <v>0.3904019842317313</v>
+        <v>0.8325835907065225</v>
       </c>
       <c r="F99">
-        <v>0.876904911024335</v>
+        <v>0.7820262761207178</v>
       </c>
       <c r="G99">
-        <v>1.399737999658915</v>
+        <v>1.357050733151345</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>1.051251576039828</v>
+        <v>0.9753243528401467</v>
       </c>
       <c r="C100">
-        <v>0.146154608200873</v>
+        <v>0.1798480930656685</v>
       </c>
       <c r="D100">
-        <v>0.3419764325237493</v>
+        <v>-0.1389238734812986</v>
       </c>
       <c r="E100">
-        <v>0.7323686282913453</v>
+        <v>0.8895103055848811</v>
       </c>
       <c r="F100">
-        <v>0.7894045619672737</v>
+        <v>0.6855862421169637</v>
       </c>
       <c r="G100">
-        <v>1.399953749155098</v>
+        <v>1.387509746849271</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>1.208685973179271</v>
+        <v>1.046733025325293</v>
       </c>
       <c r="C101">
-        <v>0.1504504726281025</v>
+        <v>0.1519852005876583</v>
       </c>
       <c r="D101">
-        <v>1.259775350806398</v>
+        <v>0.3005155045233052</v>
       </c>
       <c r="E101">
-        <v>0.2077504141853137</v>
+        <v>0.7637839717554959</v>
       </c>
       <c r="F101">
-        <v>0.9000151244324763</v>
+        <v>0.7770802826328493</v>
       </c>
       <c r="G101">
-        <v>1.623219146102168</v>
+        <v>1.409957311739316</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="O101">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="102">
@@ -6738,22 +6738,22 @@
         </is>
       </c>
       <c r="B102">
-        <v>1.561984685103161</v>
+        <v>0.8304388791686169</v>
       </c>
       <c r="C102">
-        <v>1.082162486642437</v>
+        <v>1.101923617107035</v>
       </c>
       <c r="D102">
-        <v>0.4120982312754178</v>
+        <v>-0.1686150881730429</v>
       </c>
       <c r="E102">
-        <v>0.6802674250340216</v>
+        <v>0.8660994118513623</v>
       </c>
       <c r="F102">
-        <v>0.1873002654025213</v>
+        <v>0.09579626798279908</v>
       </c>
       <c r="G102">
-        <v>13.02612226017688</v>
+        <v>7.19891021389953</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="O102">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="103">
@@ -6801,22 +6801,22 @@
         </is>
       </c>
       <c r="B103">
-        <v>1.388939041663624</v>
+        <v>1.29178936649969</v>
       </c>
       <c r="C103">
-        <v>0.7994434710367259</v>
+        <v>0.9704227592517367</v>
       </c>
       <c r="D103">
-        <v>0.4109611100980552</v>
+        <v>0.2638317790919724</v>
       </c>
       <c r="E103">
-        <v>0.681101051427169</v>
+        <v>0.7919095457248226</v>
       </c>
       <c r="F103">
-        <v>0.2898649266757616</v>
+        <v>0.1928263386527598</v>
       </c>
       <c r="G103">
-        <v>6.655346969988493</v>
+        <v>8.654003281194321</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="O103">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="104">
@@ -6864,22 +6864,22 @@
         </is>
       </c>
       <c r="B104">
-        <v>2.315078610997228</v>
+        <v>1.474968705914825</v>
       </c>
       <c r="C104">
-        <v>0.9549490171091619</v>
+        <v>1.190611845148935</v>
       </c>
       <c r="D104">
-        <v>0.8790455083529646</v>
+        <v>0.3264176942479238</v>
       </c>
       <c r="E104">
-        <v>0.3793766014919764</v>
+        <v>0.744108351961867</v>
       </c>
       <c r="F104">
-        <v>0.3562145588029662</v>
+        <v>0.1429987252895702</v>
       </c>
       <c r="G104">
-        <v>15.04595711390172</v>
+        <v>15.21365088410846</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="O104">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="105">
@@ -6927,22 +6927,22 @@
         </is>
       </c>
       <c r="B105">
-        <v>2.359556232374562</v>
+        <v>1.491693025283419</v>
       </c>
       <c r="C105">
-        <v>0.9852312387260981</v>
+        <v>0.9994649738084063</v>
       </c>
       <c r="D105">
-        <v>0.8713422093039833</v>
+        <v>0.4001258112726127</v>
       </c>
       <c r="E105">
-        <v>0.3835673300895309</v>
+        <v>0.6890638540411855</v>
       </c>
       <c r="F105">
-        <v>0.342136951148602</v>
+        <v>0.210345551135189</v>
       </c>
       <c r="G105">
-        <v>16.27273989274394</v>
+        <v>10.57853645903401</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="O105">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="106">
@@ -6990,22 +6990,22 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.09629856715337</v>
+        <v>0.5869901083232704</v>
       </c>
       <c r="C106">
-        <v>0.9311198631301209</v>
+        <v>0.9450289707868339</v>
       </c>
       <c r="D106">
-        <v>0.09874084997431813</v>
+        <v>-0.5637364853381137</v>
       </c>
       <c r="E106">
-        <v>0.9213440337403001</v>
+        <v>0.5729334829948014</v>
       </c>
       <c r="F106">
-        <v>0.1767494951839842</v>
+        <v>0.09209173698348705</v>
       </c>
       <c r="G106">
-        <v>6.79985279217611</v>
+        <v>3.741458230190045</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="O106">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="107">
@@ -7053,22 +7053,22 @@
         </is>
       </c>
       <c r="B107">
-        <v>1.563414756861602</v>
+        <v>1.197168443207195</v>
       </c>
       <c r="C107">
-        <v>0.6848333779357635</v>
+        <v>0.8324374667385485</v>
       </c>
       <c r="D107">
-        <v>0.6525271549425704</v>
+        <v>0.2161833711339315</v>
       </c>
       <c r="E107">
-        <v>0.5140611609567085</v>
+        <v>0.8288448149933829</v>
       </c>
       <c r="F107">
-        <v>0.4084538356671472</v>
+        <v>0.2341980119893101</v>
       </c>
       <c r="G107">
-        <v>5.984190840025498</v>
+        <v>6.119660321781712</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O107">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="108">
@@ -7116,22 +7116,22 @@
         </is>
       </c>
       <c r="B108">
-        <v>1.427451448095116</v>
+        <v>0.9582410073176986</v>
       </c>
       <c r="C108">
-        <v>0.8335540829984964</v>
+        <v>1.03913775335327</v>
       </c>
       <c r="D108">
-        <v>0.4269556797647571</v>
+        <v>-0.04104937878773825</v>
       </c>
       <c r="E108">
-        <v>0.6694116092146043</v>
+        <v>0.9672565304316016</v>
       </c>
       <c r="F108">
-        <v>0.2786370244773793</v>
+        <v>0.1250141271584369</v>
       </c>
       <c r="G108">
-        <v>7.312802885728003</v>
+        <v>7.344976515666286</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="O108">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="109">
@@ -7179,22 +7179,22 @@
         </is>
       </c>
       <c r="B109">
-        <v>2.491456732105958</v>
+        <v>1.357352750372635</v>
       </c>
       <c r="C109">
-        <v>0.855178688299571</v>
+        <v>0.8803606072181838</v>
       </c>
       <c r="D109">
-        <v>1.067458280796214</v>
+        <v>0.3470581182949586</v>
       </c>
       <c r="E109">
-        <v>0.2857649429481753</v>
+        <v>0.7285476569282519</v>
       </c>
       <c r="F109">
-        <v>0.4661481126612445</v>
+        <v>0.2417288131982529</v>
       </c>
       <c r="G109">
-        <v>13.31627540551056</v>
+        <v>7.621790983738103</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.9123782481839591</v>
+        <v>0.9257140967450299</v>
       </c>
       <c r="C110">
-        <v>0.05233897531774587</v>
+        <v>0.06012937222833793</v>
       </c>
       <c r="D110">
-        <v>-1.752052433556947</v>
+        <v>-1.283729398196309</v>
       </c>
       <c r="E110">
-        <v>0.07976479230920802</v>
+        <v>0.1992366543548507</v>
       </c>
       <c r="F110">
-        <v>0.8234247303344375</v>
+        <v>0.82280071945514</v>
       </c>
       <c r="G110">
-        <v>1.010941300513446</v>
+        <v>1.041499561983779</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>1.024116753318423</v>
+        <v>1.011182910022131</v>
       </c>
       <c r="C111">
-        <v>0.05474081540232654</v>
+        <v>0.05629948053404636</v>
       </c>
       <c r="D111">
-        <v>0.4353339798696464</v>
+        <v>0.1975301276674022</v>
       </c>
       <c r="E111">
-        <v>0.6633200238128053</v>
+        <v>0.8434127073902833</v>
       </c>
       <c r="F111">
-        <v>0.9199283525428302</v>
+        <v>0.9055397442099378</v>
       </c>
       <c r="G111">
-        <v>1.140105228334765</v>
+        <v>1.129150745794074</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.9805323675481545</v>
+        <v>0.9921580020893314</v>
       </c>
       <c r="C112">
-        <v>0.05618249932824451</v>
+        <v>0.05692316196677777</v>
       </c>
       <c r="D112">
-        <v>-0.3499243155392054</v>
+        <v>-0.1383076380270835</v>
       </c>
       <c r="E112">
-        <v>0.7263954981276638</v>
+        <v>0.8899972892542201</v>
       </c>
       <c r="F112">
-        <v>0.8782927630060475</v>
+        <v>0.8874170245912282</v>
       </c>
       <c r="G112">
-        <v>1.094673398558983</v>
+        <v>1.109261456374841</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.9975399489205394</v>
+        <v>0.9717231678004999</v>
       </c>
       <c r="C113">
-        <v>0.05192190730361627</v>
+        <v>0.06081819919259451</v>
       </c>
       <c r="D113">
-        <v>-0.04743820296334126</v>
+        <v>-0.4716404342329803</v>
       </c>
       <c r="E113">
-        <v>0.9621639817179418</v>
+        <v>0.6371834604815723</v>
       </c>
       <c r="F113">
-        <v>0.9010197060524229</v>
+        <v>0.8625296085618045</v>
       </c>
       <c r="G113">
-        <v>1.10439976285546</v>
+        <v>1.094740291193817</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="O113">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="114">
@@ -7494,22 +7494,22 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.7422249983286227</v>
+        <v>0.6899015670014633</v>
       </c>
       <c r="C114">
-        <v>0.5950668077506146</v>
+        <v>0.6504312989257965</v>
       </c>
       <c r="D114">
-        <v>-0.500956944075558</v>
+        <v>-0.5707080035968688</v>
       </c>
       <c r="E114">
-        <v>0.6164014250722537</v>
+        <v>0.5681975925483991</v>
       </c>
       <c r="F114">
-        <v>0.2312138217955831</v>
+        <v>0.1928141960794161</v>
       </c>
       <c r="G114">
-        <v>2.382634151651083</v>
+        <v>2.468512079655354</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="O114">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="115">
@@ -7557,22 +7557,22 @@
         </is>
       </c>
       <c r="B115">
-        <v>0.9574288809116465</v>
+        <v>0.9581354550616871</v>
       </c>
       <c r="C115">
-        <v>0.5936611809554598</v>
+        <v>0.6234646310481922</v>
       </c>
       <c r="D115">
-        <v>-0.07328058140199575</v>
+        <v>-0.06859429594575893</v>
       </c>
       <c r="E115">
-        <v>0.9415828439448164</v>
+        <v>0.9453125593499709</v>
       </c>
       <c r="F115">
-        <v>0.2990757568810486</v>
+        <v>0.2823142858197995</v>
       </c>
       <c r="G115">
-        <v>3.065009586745993</v>
+        <v>3.251778589880635</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="O115">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="116">
@@ -7620,22 +7620,22 @@
         </is>
       </c>
       <c r="B116">
-        <v>1.207351146230226</v>
+        <v>0.9874001945236787</v>
       </c>
       <c r="C116">
-        <v>0.6279723059566653</v>
+        <v>0.6545027959286365</v>
       </c>
       <c r="D116">
-        <v>0.3000591312942218</v>
+        <v>-0.01937326506520043</v>
       </c>
       <c r="E116">
-        <v>0.7641320521119194</v>
+        <v>0.9845433377926829</v>
       </c>
       <c r="F116">
-        <v>0.3526164776146327</v>
+        <v>0.2737659419940537</v>
       </c>
       <c r="G116">
-        <v>4.133944052088593</v>
+        <v>3.56128719680761</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="O116">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="117">
@@ -7683,22 +7683,22 @@
         </is>
       </c>
       <c r="B117">
-        <v>0.86634406685092</v>
+        <v>0.7564056198242676</v>
       </c>
       <c r="C117">
-        <v>0.595169358898732</v>
+        <v>0.6423705737821911</v>
       </c>
       <c r="D117">
-        <v>-0.2410627182786572</v>
+        <v>-0.4346050767592752</v>
       </c>
       <c r="E117">
-        <v>0.809506507289542</v>
+        <v>0.6638491093949246</v>
       </c>
       <c r="F117">
-        <v>0.269824467537348</v>
+        <v>0.2147671841771507</v>
       </c>
       <c r="G117">
-        <v>2.78163077284273</v>
+        <v>2.664045086281883</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="O117">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="118">
@@ -7746,22 +7746,22 @@
         </is>
       </c>
       <c r="B118">
-        <v>0.5429860204357724</v>
+        <v>0.563960909946665</v>
       </c>
       <c r="C118">
-        <v>0.3541312273369181</v>
+        <v>0.3990691063707456</v>
       </c>
       <c r="D118">
-        <v>-1.724422070952948</v>
+        <v>-1.435266046274992</v>
       </c>
       <c r="E118">
-        <v>0.0846316760142433</v>
+        <v>0.151211299324421</v>
       </c>
       <c r="F118">
-        <v>0.2712386669540797</v>
+        <v>0.2579649865490015</v>
       </c>
       <c r="G118">
-        <v>1.086990367927859</v>
+        <v>1.232926654902661</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="O118">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="119">
@@ -7809,22 +7809,22 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.043215419812787</v>
+        <v>1.041885685643467</v>
       </c>
       <c r="C119">
-        <v>0.3567645159272254</v>
+        <v>0.3739468975951873</v>
       </c>
       <c r="D119">
-        <v>0.1185871673176651</v>
+        <v>0.1097274262754853</v>
       </c>
       <c r="E119">
-        <v>0.9056024326016123</v>
+        <v>0.9126255487237932</v>
       </c>
       <c r="F119">
-        <v>0.5184364059743369</v>
+        <v>0.5006288750423747</v>
       </c>
       <c r="G119">
-        <v>2.099193651514208</v>
+        <v>2.168324353757812</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="O119">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="120">
@@ -7872,22 +7872,22 @@
         </is>
       </c>
       <c r="B120">
-        <v>0.8976615997836381</v>
+        <v>0.8489158229486942</v>
       </c>
       <c r="C120">
-        <v>0.3692569497006838</v>
+        <v>0.3850259959949761</v>
       </c>
       <c r="D120">
-        <v>-0.2923766754993291</v>
+        <v>-0.4254134727536329</v>
       </c>
       <c r="E120">
-        <v>0.7699986397460175</v>
+        <v>0.6705352863165202</v>
       </c>
       <c r="F120">
-        <v>0.4353119224256011</v>
+        <v>0.39914427685744</v>
       </c>
       <c r="G120">
-        <v>1.851078057398803</v>
+        <v>1.805507722988226</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="O120">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="121">
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="B121">
-        <v>0.8650113177587331</v>
+        <v>0.8343946077216355</v>
       </c>
       <c r="C121">
-        <v>0.3539125254348999</v>
+        <v>0.4051895792591283</v>
       </c>
       <c r="D121">
-        <v>-0.4097416101436794</v>
+        <v>-0.4468250099362923</v>
       </c>
       <c r="E121">
-        <v>0.6819955029052075</v>
+        <v>0.6550014119930653</v>
       </c>
       <c r="F121">
-        <v>0.4322857325011185</v>
+        <v>0.3771147278075925</v>
       </c>
       <c r="G121">
-        <v>1.730902788582697</v>
+        <v>1.846160624493449</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7782</v>
+        <v>7747</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>1.097133545672635</v>
+        <v>1.045814543132709</v>
       </c>
       <c r="C122">
-        <v>0.07427291770227901</v>
+        <v>0.07429965482296183</v>
       </c>
       <c r="D122">
-        <v>1.248111881408937</v>
+        <v>0.6029105923766503</v>
       </c>
       <c r="E122">
-        <v>0.2119900877595265</v>
+        <v>0.546568169028969</v>
       </c>
       <c r="F122">
-        <v>0.9485020458550696</v>
+        <v>0.904087981539316</v>
       </c>
       <c r="G122">
-        <v>1.269055794133871</v>
+        <v>1.20975843165803</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.9674515472464357</v>
+        <v>0.9846302189724785</v>
       </c>
       <c r="C123">
-        <v>0.04513067311760613</v>
+        <v>0.04185794040455506</v>
       </c>
       <c r="D123">
-        <v>-0.7332027956125449</v>
+        <v>-0.370040196814115</v>
       </c>
       <c r="E123">
-        <v>0.463434750524116</v>
+        <v>0.7113525401105544</v>
       </c>
       <c r="F123">
-        <v>0.8855517077611182</v>
+        <v>0.907075876173852</v>
       </c>
       <c r="G123">
-        <v>1.056925855448751</v>
+        <v>1.068815402966328</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>1.073374900890058</v>
+        <v>1.007496804048765</v>
       </c>
       <c r="C124">
-        <v>0.0771071150119441</v>
+        <v>0.07733080187756222</v>
       </c>
       <c r="D124">
-        <v>0.9183043311200103</v>
+        <v>0.0965830237407914</v>
       </c>
       <c r="E124">
-        <v>0.3584595604354425</v>
+        <v>0.923057538550965</v>
       </c>
       <c r="F124">
-        <v>0.9228215771461488</v>
+        <v>0.8658039827517298</v>
       </c>
       <c r="G124">
-        <v>1.248490180977073</v>
+        <v>1.172378310090937</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="O124">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="125">
@@ -8187,22 +8187,22 @@
         </is>
       </c>
       <c r="B125">
-        <v>1.622003176577127</v>
+        <v>1.402314935356395</v>
       </c>
       <c r="C125">
-        <v>0.5119765515288395</v>
+        <v>0.5450429606082595</v>
       </c>
       <c r="D125">
-        <v>0.9446954409909528</v>
+        <v>0.6203628351252941</v>
       </c>
       <c r="E125">
-        <v>0.3448143852263612</v>
+        <v>0.535018934802735</v>
       </c>
       <c r="F125">
-        <v>0.5946432174648879</v>
+        <v>0.4818414425036358</v>
       </c>
       <c r="G125">
-        <v>4.424324077961317</v>
+        <v>4.081191455234308</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="O125">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="126">
@@ -8250,22 +8250,22 @@
         </is>
       </c>
       <c r="B126">
-        <v>0.8917284977538209</v>
+        <v>0.9481824462304904</v>
       </c>
       <c r="C126">
-        <v>0.2755563853658901</v>
+        <v>0.2647184675564362</v>
       </c>
       <c r="D126">
-        <v>-0.4158625005071123</v>
+        <v>-0.2009997334356844</v>
       </c>
       <c r="E126">
-        <v>0.6775106210451609</v>
+        <v>0.8406987825017627</v>
       </c>
       <c r="F126">
-        <v>0.5196113459585541</v>
+        <v>0.5643689899706205</v>
       </c>
       <c r="G126">
-        <v>1.530335547695512</v>
+        <v>1.593017985248337</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="O126">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="127">
@@ -8313,22 +8313,22 @@
         </is>
       </c>
       <c r="B127">
-        <v>1.397016475242222</v>
+        <v>1.119640703565869</v>
       </c>
       <c r="C127">
-        <v>0.5282478358072044</v>
+        <v>0.556212430703185</v>
       </c>
       <c r="D127">
-        <v>0.6329204794486422</v>
+        <v>0.2031738724520515</v>
       </c>
       <c r="E127">
-        <v>0.52678557340863</v>
+        <v>0.8389991336837049</v>
       </c>
       <c r="F127">
-        <v>0.4960850676586813</v>
+        <v>0.3763828263103758</v>
       </c>
       <c r="G127">
-        <v>3.934113641656694</v>
+        <v>3.330638959726936</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="O127">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="128">
@@ -8376,22 +8376,22 @@
         </is>
       </c>
       <c r="B128">
-        <v>1.709891324720098</v>
+        <v>1.395411088780992</v>
       </c>
       <c r="C128">
-        <v>0.4346482730495272</v>
+        <v>0.4553069808358044</v>
       </c>
       <c r="D128">
-        <v>1.234169900034584</v>
+        <v>0.7317899201723727</v>
       </c>
       <c r="E128">
-        <v>0.2171396010324459</v>
+        <v>0.4642968023379379</v>
       </c>
       <c r="F128">
-        <v>0.7294494952531385</v>
+        <v>0.5716683718720545</v>
       </c>
       <c r="G128">
-        <v>4.00812991355685</v>
+        <v>3.406121805053701</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="O128">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="129">
@@ -8439,22 +8439,22 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.8465199888276945</v>
+        <v>0.9254496440896567</v>
       </c>
       <c r="C129">
-        <v>0.2543507747815161</v>
+        <v>0.2456153318510145</v>
       </c>
       <c r="D129">
-        <v>-0.6550853416150685</v>
+        <v>-0.3154345344667889</v>
       </c>
       <c r="E129">
-        <v>0.5124128091847912</v>
+        <v>0.7524317494556281</v>
       </c>
       <c r="F129">
-        <v>0.5142016258777289</v>
+        <v>0.5718533152618002</v>
       </c>
       <c r="G129">
-        <v>1.393609151393929</v>
+        <v>1.497686593551666</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="O129">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="130">
@@ -8502,22 +8502,22 @@
         </is>
       </c>
       <c r="B130">
-        <v>1.513252806455312</v>
+        <v>1.134066771112026</v>
       </c>
       <c r="C130">
-        <v>0.4530711611072129</v>
+        <v>0.4738294428205274</v>
       </c>
       <c r="D130">
-        <v>0.9143409378861889</v>
+        <v>0.2655176594227837</v>
       </c>
       <c r="E130">
-        <v>0.3605377258509442</v>
+        <v>0.7906107076676494</v>
       </c>
       <c r="F130">
-        <v>0.6226680994451937</v>
+        <v>0.4480374043858958</v>
       </c>
       <c r="G130">
-        <v>3.677615825004111</v>
+        <v>2.870535872118229</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.9921052135992737</v>
+        <v>0.9843380590385147</v>
       </c>
       <c r="C131">
-        <v>0.03231664454743537</v>
+        <v>0.03063984484228595</v>
       </c>
       <c r="D131">
-        <v>-0.2452641769096542</v>
+        <v>-0.5152077329214856</v>
       </c>
       <c r="E131">
-        <v>0.8062518874297211</v>
+        <v>0.6064078659135681</v>
       </c>
       <c r="F131">
-        <v>0.9312145523163665</v>
+        <v>0.9269655496448328</v>
       </c>
       <c r="G131">
-        <v>1.056977419867971</v>
+        <v>1.045261514673283</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.996258469347895</v>
+        <v>0.9906908575051315</v>
       </c>
       <c r="C132">
-        <v>0.02704769951401859</v>
+        <v>0.02487328297686713</v>
       </c>
       <c r="D132">
-        <v>-0.1385902591977027</v>
+        <v>-0.3760156378496571</v>
       </c>
       <c r="E132">
-        <v>0.8897739410584836</v>
+        <v>0.7069052703912913</v>
       </c>
       <c r="F132">
-        <v>0.9448197932953988</v>
+        <v>0.9435523015393471</v>
       </c>
       <c r="G132">
-        <v>1.050497613185687</v>
+        <v>1.040184389930529</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.9675514362187615</v>
+        <v>0.9498081476911503</v>
       </c>
       <c r="C133">
-        <v>0.03497400266878728</v>
+        <v>0.03376580794019161</v>
       </c>
       <c r="D133">
-        <v>-0.9431774725172624</v>
+        <v>-1.525071299112944</v>
       </c>
       <c r="E133">
-        <v>0.3455901340672276</v>
+        <v>0.1272413149653025</v>
       </c>
       <c r="F133">
-        <v>0.9034500304980402</v>
+        <v>0.8889848972767683</v>
       </c>
       <c r="G133">
-        <v>1.036200952047031</v>
+        <v>1.014792849894312</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="O133">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="134">
@@ -8754,22 +8754,22 @@
         </is>
       </c>
       <c r="B134">
-        <v>1.170934281951812</v>
+        <v>1.009022621838719</v>
       </c>
       <c r="C134">
-        <v>0.4231219619138541</v>
+        <v>0.4228388530592445</v>
       </c>
       <c r="D134">
-        <v>0.3729467528036776</v>
+        <v>0.02124251618165114</v>
       </c>
       <c r="E134">
-        <v>0.7091880744681234</v>
+        <v>0.9830521989159603</v>
       </c>
       <c r="F134">
-        <v>0.5109406477796894</v>
+        <v>0.4405343918487732</v>
       </c>
       <c r="G134">
-        <v>2.683456676637716</v>
+        <v>2.311117293497907</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="O134">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="135">
@@ -8817,22 +8817,22 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.9319179629435258</v>
+        <v>0.8978287049699367</v>
       </c>
       <c r="C135">
-        <v>0.2627110258038643</v>
+        <v>0.2458086304120307</v>
       </c>
       <c r="D135">
-        <v>-0.2683956280395599</v>
+        <v>-0.4384548272310756</v>
       </c>
       <c r="E135">
-        <v>0.788394804422708</v>
+        <v>0.6610566093119039</v>
       </c>
       <c r="F135">
-        <v>0.5568749114994114</v>
+        <v>0.5545756549944605</v>
       </c>
       <c r="G135">
-        <v>1.559544292125519</v>
+        <v>1.453537269817669</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="O135">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="136">
@@ -8880,22 +8880,22 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.9356548706959221</v>
+        <v>0.7522214222664885</v>
       </c>
       <c r="C136">
-        <v>0.4438749153399336</v>
+        <v>0.4404769335007028</v>
       </c>
       <c r="D136">
-        <v>-0.1498363527468684</v>
+        <v>-0.6464005994738637</v>
       </c>
       <c r="E136">
-        <v>0.8808937277614407</v>
+        <v>0.518019952280661</v>
       </c>
       <c r="F136">
-        <v>0.3920023492999971</v>
+        <v>0.3172568821269798</v>
       </c>
       <c r="G136">
-        <v>2.233277526576826</v>
+        <v>1.78352968838087</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="O136">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="137">
@@ -8943,22 +8943,22 @@
         </is>
       </c>
       <c r="B137">
-        <v>0.962602884706977</v>
+        <v>0.9173420852246739</v>
       </c>
       <c r="C137">
-        <v>0.2382508986585848</v>
+        <v>0.2319481632866935</v>
       </c>
       <c r="D137">
-        <v>-0.159975578457033</v>
+        <v>-0.3719573668564159</v>
       </c>
       <c r="E137">
-        <v>0.8729003120009485</v>
+        <v>0.7099245918521497</v>
       </c>
       <c r="F137">
-        <v>0.6034588019450305</v>
+        <v>0.5822328214517491</v>
       </c>
       <c r="G137">
-        <v>1.53548893588033</v>
+        <v>1.445326457594921</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="O137">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="138">
@@ -9006,22 +9006,22 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.9669924214241634</v>
+        <v>0.9162937666752783</v>
       </c>
       <c r="C138">
-        <v>0.1779005465547511</v>
+        <v>0.1672594999035715</v>
       </c>
       <c r="D138">
-        <v>-0.1886707006421571</v>
+        <v>-0.5226504909807612</v>
       </c>
       <c r="E138">
-        <v>0.8503509166301924</v>
+        <v>0.6012174972078542</v>
       </c>
       <c r="F138">
-        <v>0.6823290327012447</v>
+        <v>0.6601812531834392</v>
       </c>
       <c r="G138">
-        <v>1.370415588781177</v>
+        <v>1.271763266223311</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="O138">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="139">
@@ -9069,22 +9069,22 @@
         </is>
       </c>
       <c r="B139">
-        <v>0.814037076356367</v>
+        <v>0.7311970769142146</v>
       </c>
       <c r="C139">
-        <v>0.2569644216358875</v>
+        <v>0.2523562074005284</v>
       </c>
       <c r="D139">
-        <v>-0.80069203494283</v>
+        <v>-1.240596614328205</v>
       </c>
       <c r="E139">
-        <v>0.4233099548134896</v>
+        <v>0.2147548033057875</v>
       </c>
       <c r="F139">
-        <v>0.4919440062595483</v>
+        <v>0.4458907401188295</v>
       </c>
       <c r="G139">
-        <v>1.347015825482395</v>
+        <v>1.19905868676575</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.103898940537185</v>
+        <v>1.064750200218215</v>
       </c>
       <c r="C140">
-        <v>0.1129287847249574</v>
+        <v>0.1322064404000388</v>
       </c>
       <c r="D140">
-        <v>0.8753162848354147</v>
+        <v>0.4745624923701888</v>
       </c>
       <c r="E140">
-        <v>0.3814018357783266</v>
+        <v>0.6350988456952205</v>
       </c>
       <c r="F140">
-        <v>0.884716568737507</v>
+        <v>0.8217002220236255</v>
       </c>
       <c r="G140">
-        <v>1.377382219322574</v>
+        <v>1.379691715395609</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.040530967205894</v>
+        <v>1.078534591186399</v>
       </c>
       <c r="C141">
-        <v>0.09418464673182288</v>
+        <v>0.1012643647862907</v>
       </c>
       <c r="D141">
-        <v>0.4218429397812253</v>
+        <v>0.7465929393326314</v>
       </c>
       <c r="E141">
-        <v>0.6731396611507789</v>
+        <v>0.4553093117284188</v>
       </c>
       <c r="F141">
-        <v>0.8651370137184785</v>
+        <v>0.8843775204789988</v>
       </c>
       <c r="G141">
-        <v>1.251483495152772</v>
+        <v>1.315317087385461</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>1.198373226444288</v>
+        <v>1.089038837895153</v>
       </c>
       <c r="C142">
-        <v>0.120363990645699</v>
+        <v>0.1403393139040735</v>
       </c>
       <c r="D142">
-        <v>1.503481161399825</v>
+        <v>0.6077805623929051</v>
       </c>
       <c r="E142">
-        <v>0.1327150112855618</v>
+        <v>0.5433330226757267</v>
       </c>
       <c r="F142">
-        <v>0.94653806339053</v>
+        <v>0.827153910933688</v>
       </c>
       <c r="G142">
-        <v>1.517211452347033</v>
+        <v>1.433839065217339</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="O142">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="143">
@@ -9321,22 +9321,22 @@
         </is>
       </c>
       <c r="B143">
-        <v>1.217049268504742</v>
+        <v>1.388294750273747</v>
       </c>
       <c r="C143">
-        <v>0.7318993946922723</v>
+        <v>0.8729510590745108</v>
       </c>
       <c r="D143">
-        <v>0.2683829200850531</v>
+        <v>0.3758242712862656</v>
       </c>
       <c r="E143">
-        <v>0.7884045852139284</v>
+        <v>0.7070475425037452</v>
       </c>
       <c r="F143">
-        <v>0.2899440930573214</v>
+        <v>0.2508559421161227</v>
       </c>
       <c r="G143">
-        <v>5.108601821645299</v>
+        <v>7.683143948591254</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="O143">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="144">
@@ -9384,22 +9384,22 @@
         </is>
       </c>
       <c r="B144">
-        <v>1.707929172910611</v>
+        <v>1.749691813620089</v>
       </c>
       <c r="C144">
-        <v>0.6015474043984956</v>
+        <v>0.6318371312639565</v>
       </c>
       <c r="D144">
-        <v>0.8898411376088901</v>
+        <v>0.8854175201842228</v>
       </c>
       <c r="E144">
-        <v>0.3735511940286017</v>
+        <v>0.375931486446703</v>
       </c>
       <c r="F144">
-        <v>0.5253294859497422</v>
+        <v>0.5071551251375939</v>
       </c>
       <c r="G144">
-        <v>5.552747633050605</v>
+        <v>6.036459637115129</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="O144">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="145">
@@ -9447,22 +9447,22 @@
         </is>
       </c>
       <c r="B145">
-        <v>1.807793541518414</v>
+        <v>1.611763585794822</v>
       </c>
       <c r="C145">
-        <v>0.7485273088666288</v>
+        <v>0.886541811549337</v>
       </c>
       <c r="D145">
-        <v>0.7910293409442973</v>
+        <v>0.5384167652042934</v>
       </c>
       <c r="E145">
-        <v>0.4289268698933013</v>
+        <v>0.5902893545633969</v>
       </c>
       <c r="F145">
-        <v>0.4168705641820152</v>
+        <v>0.2835799891218367</v>
       </c>
       <c r="G145">
-        <v>7.839645610786647</v>
+        <v>9.160667029217199</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="O145">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="146">
@@ -9510,22 +9510,22 @@
         </is>
       </c>
       <c r="B146">
-        <v>1.521376784812899</v>
+        <v>1.466421674113632</v>
       </c>
       <c r="C146">
-        <v>0.6265660458539191</v>
+        <v>0.7517739648342484</v>
       </c>
       <c r="D146">
-        <v>0.6697070598483963</v>
+        <v>0.5092291244890935</v>
       </c>
       <c r="E146">
-        <v>0.50304455032638</v>
+        <v>0.6105916307791115</v>
       </c>
       <c r="F146">
-        <v>0.4455565164319238</v>
+        <v>0.3360065256387034</v>
       </c>
       <c r="G146">
-        <v>5.194823184055659</v>
+        <v>6.399853461841607</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="O146">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="147">
@@ -9573,22 +9573,22 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.341071750178672</v>
+        <v>1.561618504677224</v>
       </c>
       <c r="C147">
-        <v>0.5342536063394875</v>
+        <v>0.5782766778558204</v>
       </c>
       <c r="D147">
-        <v>0.5493067419035536</v>
+        <v>0.770777732344468</v>
       </c>
       <c r="E147">
-        <v>0.5827949614099837</v>
+        <v>0.4408386881743289</v>
       </c>
       <c r="F147">
-        <v>0.4706461603595102</v>
+        <v>0.5027417424281738</v>
       </c>
       <c r="G147">
-        <v>3.821285693170203</v>
+        <v>4.850705935759327</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="O147">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="148">
@@ -9636,22 +9636,22 @@
         </is>
       </c>
       <c r="B148">
-        <v>2.358274476184527</v>
+        <v>1.69320520350805</v>
       </c>
       <c r="C148">
-        <v>0.6565257406203897</v>
+        <v>0.7864147209642071</v>
       </c>
       <c r="D148">
-        <v>1.306773130698804</v>
+        <v>0.6696508709730593</v>
       </c>
       <c r="E148">
-        <v>0.1912897731911795</v>
+        <v>0.5030803769924523</v>
       </c>
       <c r="F148">
-        <v>0.6512663314902879</v>
+        <v>0.3625034718694974</v>
       </c>
       <c r="G148">
-        <v>8.539453424986919</v>
+        <v>7.908734905079327</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.9680304651924806</v>
+        <v>0.9651453111082083</v>
       </c>
       <c r="C149">
-        <v>0.04479310045313847</v>
+        <v>0.04357584150522664</v>
       </c>
       <c r="D149">
-        <v>-0.7253733178955368</v>
+        <v>-0.814134765839522</v>
       </c>
       <c r="E149">
-        <v>0.4682230374969344</v>
+        <v>0.4155677513439811</v>
       </c>
       <c r="F149">
-        <v>0.8866680696723144</v>
+        <v>0.8861370224412167</v>
       </c>
       <c r="G149">
-        <v>1.056858833190066</v>
+        <v>1.051198006588144</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.023245835058003</v>
+        <v>1.0323096683386</v>
       </c>
       <c r="C150">
-        <v>0.05010297718135673</v>
+        <v>0.04741209275992862</v>
       </c>
       <c r="D150">
-        <v>0.4586507103472363</v>
+        <v>0.6706872955195998</v>
       </c>
       <c r="E150">
-        <v>0.646485014740346</v>
+        <v>0.5024197578727547</v>
       </c>
       <c r="F150">
-        <v>0.9275391596740811</v>
+        <v>0.9407034749815493</v>
       </c>
       <c r="G150">
-        <v>1.128827853835795</v>
+        <v>1.132836520420266</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.9666937544495358</v>
+        <v>0.9279871958549404</v>
       </c>
       <c r="C151">
-        <v>0.04882543403483839</v>
+        <v>0.05002448325995696</v>
       </c>
       <c r="D151">
-        <v>-0.693768133218617</v>
+        <v>-1.494015309920374</v>
       </c>
       <c r="E151">
-        <v>0.4878276300807148</v>
+        <v>0.1351716177328971</v>
       </c>
       <c r="F151">
-        <v>0.8784734248046667</v>
+        <v>0.8413197161212536</v>
       </c>
       <c r="G151">
-        <v>1.06377357414031</v>
+        <v>1.023582615703972</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="O151">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="152">
@@ -9888,22 +9888,22 @@
         </is>
       </c>
       <c r="B152">
-        <v>0.8807246045164402</v>
+        <v>0.8414564441645382</v>
       </c>
       <c r="C152">
-        <v>0.5710910661891817</v>
+        <v>0.5826887110330968</v>
       </c>
       <c r="D152">
-        <v>-0.222399374855735</v>
+        <v>-0.2962491347082061</v>
       </c>
       <c r="E152">
-        <v>0.8240029984291238</v>
+        <v>0.7670398278735816</v>
       </c>
       <c r="F152">
-        <v>0.2875587137863695</v>
+        <v>0.2685629574096456</v>
       </c>
       <c r="G152">
-        <v>2.69745200479961</v>
+        <v>2.636435621112202</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="O152">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="153">
@@ -9951,22 +9951,22 @@
         </is>
       </c>
       <c r="B153">
-        <v>1.415821168629488</v>
+        <v>1.242408477974664</v>
       </c>
       <c r="C153">
-        <v>0.5401819448722234</v>
+        <v>0.5152753719527148</v>
       </c>
       <c r="D153">
-        <v>0.6436899590143539</v>
+        <v>0.4212346029179713</v>
       </c>
       <c r="E153">
-        <v>0.5197765023567671</v>
+        <v>0.6735837789970486</v>
       </c>
       <c r="F153">
-        <v>0.4911393106137746</v>
+        <v>0.45254442021014</v>
       </c>
       <c r="G153">
-        <v>4.081427689089461</v>
+        <v>3.410889091122939</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="O153">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="154">
@@ -10014,22 +10014,22 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.8754170895127839</v>
+        <v>0.6754689688828175</v>
       </c>
       <c r="C154">
-        <v>0.5937956545106745</v>
+        <v>0.6122779627000374</v>
       </c>
       <c r="D154">
-        <v>-0.2240751198795894</v>
+        <v>-0.6408005587922674</v>
       </c>
       <c r="E154">
-        <v>0.8226988517272378</v>
+        <v>0.5216522698430035</v>
       </c>
       <c r="F154">
-        <v>0.2733853530438196</v>
+        <v>0.2034386454632037</v>
       </c>
       <c r="G154">
-        <v>2.803204605069674</v>
+        <v>2.242731841262386</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         </is>
       </c>
       <c r="O154">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="155">
@@ -10077,22 +10077,22 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.7936299011131795</v>
+        <v>0.7857931618344638</v>
       </c>
       <c r="C155">
-        <v>0.3212658825126872</v>
+        <v>0.3211828904546778</v>
       </c>
       <c r="D155">
-        <v>-0.7194602928250583</v>
+        <v>-0.750543323540155</v>
       </c>
       <c r="E155">
-        <v>0.4718573591828188</v>
+        <v>0.4529275413212864</v>
       </c>
       <c r="F155">
-        <v>0.4228204724261528</v>
+        <v>0.4187134129131507</v>
       </c>
       <c r="G155">
-        <v>1.489635580620852</v>
+        <v>1.474686203362392</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="O155">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="156">
@@ -10140,22 +10140,22 @@
         </is>
       </c>
       <c r="B156">
-        <v>1.162968854449588</v>
+        <v>1.140540376275274</v>
       </c>
       <c r="C156">
-        <v>0.3325244263455904</v>
+        <v>0.322732152743108</v>
       </c>
       <c r="D156">
-        <v>0.4540300827949657</v>
+        <v>0.4074653338874396</v>
       </c>
       <c r="E156">
-        <v>0.6498071748072967</v>
+        <v>0.6836662501121937</v>
       </c>
       <c r="F156">
-        <v>0.6060699886304002</v>
+        <v>0.6058994494645477</v>
       </c>
       <c r="G156">
-        <v>2.231584770392881</v>
+        <v>2.146944267838056</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="O156">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="157">
@@ -10203,22 +10203,22 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.7819337698621682</v>
+        <v>0.6340480380435886</v>
       </c>
       <c r="C157">
-        <v>0.3449283371075385</v>
+        <v>0.3599697323189309</v>
       </c>
       <c r="D157">
-        <v>-0.7131488162356959</v>
+        <v>-1.265746857924072</v>
       </c>
       <c r="E157">
-        <v>0.475753674783268</v>
+        <v>0.2056037264382345</v>
       </c>
       <c r="F157">
-        <v>0.3977099320833933</v>
+        <v>0.313123289917235</v>
       </c>
       <c r="G157">
-        <v>1.537352656112841</v>
+        <v>1.283893365623443</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7784</v>
+        <v>7749</v>
       </c>
     </row>
   </sheetData>
